--- a/artfynd/A 50311-2024 artfynd.xlsx
+++ b/artfynd/A 50311-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2690,6 +2690,857 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121562424</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Djupsjö NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>421365</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7051704</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121562427</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Djupsjö NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>421771</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7051696</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121562426</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Djupsjö NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>421679</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7051789</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121562435</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Djupsjö NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>421599</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7051638</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121562425</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Djupsjö NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>421399</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7051705</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121562423</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Djupsjö NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>421425</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7051623</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121562433</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90737</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Djupsjö NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>421634</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7051593</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121562422</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Djupsjö NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>421443</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7051615</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50311-2024 artfynd.xlsx
+++ b/artfynd/A 50311-2024 artfynd.xlsx
@@ -2692,10 +2692,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562424</v>
+        <v>121562435</v>
       </c>
       <c r="B19" t="n">
-        <v>57355</v>
+        <v>78608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2708,21 +2708,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421365</v>
+        <v>421599</v>
       </c>
       <c r="R19" t="n">
-        <v>7051704</v>
+        <v>7051638</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2799,7 +2799,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562427</v>
+        <v>121562425</v>
       </c>
       <c r="B20" t="n">
         <v>57355</v>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421771</v>
+        <v>421399</v>
       </c>
       <c r="R20" t="n">
-        <v>7051696</v>
+        <v>7051705</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562426</v>
+        <v>121562427</v>
       </c>
       <c r="B21" t="n">
         <v>57355</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421679</v>
+        <v>421771</v>
       </c>
       <c r="R21" t="n">
-        <v>7051789</v>
+        <v>7051696</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,10 +3013,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562435</v>
+        <v>121562423</v>
       </c>
       <c r="B22" t="n">
-        <v>78608</v>
+        <v>57355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421599</v>
+        <v>421425</v>
       </c>
       <c r="R22" t="n">
-        <v>7051638</v>
+        <v>7051623</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3120,7 +3120,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562425</v>
+        <v>121562424</v>
       </c>
       <c r="B23" t="n">
         <v>57355</v>
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421399</v>
+        <v>421365</v>
       </c>
       <c r="R23" t="n">
-        <v>7051705</v>
+        <v>7051704</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562423</v>
+        <v>121562422</v>
       </c>
       <c r="B24" t="n">
         <v>57355</v>
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421425</v>
+        <v>421443</v>
       </c>
       <c r="R24" t="n">
-        <v>7051623</v>
+        <v>7051615</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3436,7 +3436,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562422</v>
+        <v>121562426</v>
       </c>
       <c r="B26" t="n">
         <v>57355</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421443</v>
+        <v>421679</v>
       </c>
       <c r="R26" t="n">
-        <v>7051615</v>
+        <v>7051789</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 50311-2024 artfynd.xlsx
+++ b/artfynd/A 50311-2024 artfynd.xlsx
@@ -2692,10 +2692,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562435</v>
+        <v>121562426</v>
       </c>
       <c r="B19" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2708,21 +2708,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421599</v>
+        <v>421679</v>
       </c>
       <c r="R19" t="n">
-        <v>7051638</v>
+        <v>7051789</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2799,10 +2799,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562425</v>
+        <v>121562427</v>
       </c>
       <c r="B20" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421399</v>
+        <v>421771</v>
       </c>
       <c r="R20" t="n">
-        <v>7051705</v>
+        <v>7051696</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562427</v>
+        <v>121562425</v>
       </c>
       <c r="B21" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421771</v>
+        <v>421399</v>
       </c>
       <c r="R21" t="n">
-        <v>7051696</v>
+        <v>7051705</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562423</v>
+        <v>121562435</v>
       </c>
       <c r="B22" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421425</v>
+        <v>421599</v>
       </c>
       <c r="R22" t="n">
-        <v>7051623</v>
+        <v>7051638</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3120,10 +3120,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562424</v>
+        <v>121562423</v>
       </c>
       <c r="B23" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421365</v>
+        <v>421425</v>
       </c>
       <c r="R23" t="n">
-        <v>7051704</v>
+        <v>7051623</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562422</v>
+        <v>121562424</v>
       </c>
       <c r="B24" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421443</v>
+        <v>421365</v>
       </c>
       <c r="R24" t="n">
-        <v>7051615</v>
+        <v>7051704</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3337,7 +3337,7 @@
         <v>121562433</v>
       </c>
       <c r="B25" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562426</v>
+        <v>121562422</v>
       </c>
       <c r="B26" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421679</v>
+        <v>421443</v>
       </c>
       <c r="R26" t="n">
-        <v>7051789</v>
+        <v>7051615</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 50311-2024 artfynd.xlsx
+++ b/artfynd/A 50311-2024 artfynd.xlsx
@@ -2692,10 +2692,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562426</v>
+        <v>121562433</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2708,21 +2708,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421679</v>
+        <v>421634</v>
       </c>
       <c r="R19" t="n">
-        <v>7051789</v>
+        <v>7051593</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2768,11 +2768,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2906,7 +2901,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562425</v>
+        <v>121562422</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2946,10 +2941,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421399</v>
+        <v>421443</v>
       </c>
       <c r="R21" t="n">
-        <v>7051705</v>
+        <v>7051615</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3013,10 +3008,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562435</v>
+        <v>121562426</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3029,21 +3024,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3053,10 +3048,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421599</v>
+        <v>421679</v>
       </c>
       <c r="R22" t="n">
-        <v>7051638</v>
+        <v>7051789</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3093,7 +3088,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3334,10 +3329,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562433</v>
+        <v>121562425</v>
       </c>
       <c r="B25" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3350,21 +3345,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3374,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421634</v>
+        <v>421399</v>
       </c>
       <c r="R25" t="n">
-        <v>7051593</v>
+        <v>7051705</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3410,6 +3405,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3436,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562422</v>
+        <v>121562435</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3452,21 +3452,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421443</v>
+        <v>421599</v>
       </c>
       <c r="R26" t="n">
-        <v>7051615</v>
+        <v>7051638</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 50311-2024 artfynd.xlsx
+++ b/artfynd/A 50311-2024 artfynd.xlsx
@@ -2692,10 +2692,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562433</v>
+        <v>121562424</v>
       </c>
       <c r="B19" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2708,21 +2708,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421634</v>
+        <v>421365</v>
       </c>
       <c r="R19" t="n">
-        <v>7051593</v>
+        <v>7051704</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2768,6 +2768,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2794,10 +2799,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562427</v>
+        <v>121562433</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,21 +2815,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2834,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421771</v>
+        <v>421634</v>
       </c>
       <c r="R20" t="n">
-        <v>7051696</v>
+        <v>7051593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2870,11 +2875,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2901,7 +2901,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562422</v>
+        <v>121562423</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421443</v>
+        <v>421425</v>
       </c>
       <c r="R21" t="n">
-        <v>7051615</v>
+        <v>7051623</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562426</v>
+        <v>121562425</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421679</v>
+        <v>421399</v>
       </c>
       <c r="R22" t="n">
-        <v>7051789</v>
+        <v>7051705</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3115,7 +3115,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562423</v>
+        <v>121562422</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421425</v>
+        <v>421443</v>
       </c>
       <c r="R23" t="n">
-        <v>7051623</v>
+        <v>7051615</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562424</v>
+        <v>121562426</v>
       </c>
       <c r="B24" t="n">
         <v>57356</v>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421365</v>
+        <v>421679</v>
       </c>
       <c r="R24" t="n">
-        <v>7051704</v>
+        <v>7051789</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3329,7 +3329,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562425</v>
+        <v>121562427</v>
       </c>
       <c r="B25" t="n">
         <v>57356</v>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421399</v>
+        <v>421771</v>
       </c>
       <c r="R25" t="n">
-        <v>7051705</v>
+        <v>7051696</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 50311-2024 artfynd.xlsx
+++ b/artfynd/A 50311-2024 artfynd.xlsx
@@ -2692,7 +2692,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562424</v>
+        <v>121562427</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421365</v>
+        <v>421771</v>
       </c>
       <c r="R19" t="n">
-        <v>7051704</v>
+        <v>7051696</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562433</v>
+        <v>121562426</v>
       </c>
       <c r="B20" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2815,21 +2815,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421634</v>
+        <v>421679</v>
       </c>
       <c r="R20" t="n">
-        <v>7051593</v>
+        <v>7051789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2875,6 +2875,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2901,10 +2906,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562423</v>
+        <v>121562433</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2917,21 +2922,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2941,10 +2946,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421425</v>
+        <v>421634</v>
       </c>
       <c r="R21" t="n">
-        <v>7051623</v>
+        <v>7051593</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2977,11 +2982,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3008,10 +3008,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562425</v>
+        <v>121562435</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3024,21 +3024,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421399</v>
+        <v>421599</v>
       </c>
       <c r="R22" t="n">
-        <v>7051705</v>
+        <v>7051638</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3115,7 +3115,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562422</v>
+        <v>121562423</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421443</v>
+        <v>421425</v>
       </c>
       <c r="R23" t="n">
-        <v>7051615</v>
+        <v>7051623</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562426</v>
+        <v>121562425</v>
       </c>
       <c r="B24" t="n">
         <v>57356</v>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421679</v>
+        <v>421399</v>
       </c>
       <c r="R24" t="n">
-        <v>7051789</v>
+        <v>7051705</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3329,7 +3329,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562427</v>
+        <v>121562422</v>
       </c>
       <c r="B25" t="n">
         <v>57356</v>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421771</v>
+        <v>421443</v>
       </c>
       <c r="R25" t="n">
-        <v>7051696</v>
+        <v>7051615</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562435</v>
+        <v>121562424</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3452,21 +3452,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421599</v>
+        <v>421365</v>
       </c>
       <c r="R26" t="n">
-        <v>7051638</v>
+        <v>7051704</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 50311-2024 artfynd.xlsx
+++ b/artfynd/A 50311-2024 artfynd.xlsx
@@ -2692,10 +2692,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562427</v>
+        <v>121562435</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2708,21 +2708,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421771</v>
+        <v>421599</v>
       </c>
       <c r="R19" t="n">
-        <v>7051696</v>
+        <v>7051638</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2799,10 +2799,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562426</v>
+        <v>121562423</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421679</v>
+        <v>421425</v>
       </c>
       <c r="R20" t="n">
-        <v>7051789</v>
+        <v>7051623</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2906,10 +2906,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562433</v>
+        <v>121562424</v>
       </c>
       <c r="B21" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421634</v>
+        <v>421365</v>
       </c>
       <c r="R21" t="n">
-        <v>7051593</v>
+        <v>7051704</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2982,6 +2982,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3008,10 +3013,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562435</v>
+        <v>121562422</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3024,21 +3029,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3048,10 +3053,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421599</v>
+        <v>421443</v>
       </c>
       <c r="R22" t="n">
-        <v>7051638</v>
+        <v>7051615</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3088,7 +3093,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3115,10 +3120,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562423</v>
+        <v>121562433</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3131,21 +3136,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3155,10 +3160,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421425</v>
+        <v>421634</v>
       </c>
       <c r="R23" t="n">
-        <v>7051623</v>
+        <v>7051593</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3191,11 +3196,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3222,10 +3222,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562425</v>
+        <v>121562426</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421399</v>
+        <v>421679</v>
       </c>
       <c r="R24" t="n">
-        <v>7051705</v>
+        <v>7051789</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3329,10 +3329,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562422</v>
+        <v>121562427</v>
       </c>
       <c r="B25" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421443</v>
+        <v>421771</v>
       </c>
       <c r="R25" t="n">
-        <v>7051615</v>
+        <v>7051696</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562424</v>
+        <v>121562425</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421365</v>
+        <v>421399</v>
       </c>
       <c r="R26" t="n">
-        <v>7051704</v>
+        <v>7051705</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 50311-2024 artfynd.xlsx
+++ b/artfynd/A 50311-2024 artfynd.xlsx
@@ -2692,7 +2692,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562424</v>
+        <v>121562425</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421365</v>
+        <v>421399</v>
       </c>
       <c r="R19" t="n">
-        <v>7051704</v>
+        <v>7051705</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562435</v>
+        <v>121562422</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2815,21 +2815,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421599</v>
+        <v>421443</v>
       </c>
       <c r="R20" t="n">
-        <v>7051638</v>
+        <v>7051615</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2906,7 +2906,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562425</v>
+        <v>121562426</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421399</v>
+        <v>421679</v>
       </c>
       <c r="R21" t="n">
-        <v>7051705</v>
+        <v>7051789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,7 +3013,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562422</v>
+        <v>121562427</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421443</v>
+        <v>421771</v>
       </c>
       <c r="R22" t="n">
-        <v>7051615</v>
+        <v>7051696</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562427</v>
+        <v>121562424</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421771</v>
+        <v>421365</v>
       </c>
       <c r="R23" t="n">
-        <v>7051696</v>
+        <v>7051704</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562426</v>
+        <v>121562435</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3350,21 +3350,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421679</v>
+        <v>421599</v>
       </c>
       <c r="R25" t="n">
-        <v>7051789</v>
+        <v>7051638</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 50311-2024 artfynd.xlsx
+++ b/artfynd/A 50311-2024 artfynd.xlsx
@@ -2692,7 +2692,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562425</v>
+        <v>121562422</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421399</v>
+        <v>421443</v>
       </c>
       <c r="R19" t="n">
-        <v>7051705</v>
+        <v>7051615</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562422</v>
+        <v>121562427</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421443</v>
+        <v>421771</v>
       </c>
       <c r="R20" t="n">
-        <v>7051615</v>
+        <v>7051696</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562426</v>
+        <v>121562423</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421679</v>
+        <v>421425</v>
       </c>
       <c r="R21" t="n">
-        <v>7051789</v>
+        <v>7051623</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,10 +3013,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562427</v>
+        <v>121562433</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421771</v>
+        <v>421634</v>
       </c>
       <c r="R22" t="n">
-        <v>7051696</v>
+        <v>7051593</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3089,11 +3089,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3120,7 +3115,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562424</v>
+        <v>121562425</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -3160,10 +3155,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421365</v>
+        <v>421399</v>
       </c>
       <c r="R23" t="n">
-        <v>7051704</v>
+        <v>7051705</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3227,7 +3222,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562423</v>
+        <v>121562424</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3267,10 +3262,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421425</v>
+        <v>421365</v>
       </c>
       <c r="R24" t="n">
-        <v>7051623</v>
+        <v>7051704</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3334,10 +3329,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562435</v>
+        <v>121562426</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3350,21 +3345,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3374,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421599</v>
+        <v>421679</v>
       </c>
       <c r="R25" t="n">
-        <v>7051638</v>
+        <v>7051789</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3414,7 +3409,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3441,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562433</v>
+        <v>121562435</v>
       </c>
       <c r="B26" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3457,21 +3452,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3481,10 +3476,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421634</v>
+        <v>421599</v>
       </c>
       <c r="R26" t="n">
-        <v>7051593</v>
+        <v>7051638</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3517,6 +3512,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 50311-2024 artfynd.xlsx
+++ b/artfynd/A 50311-2024 artfynd.xlsx
@@ -2799,10 +2799,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562427</v>
+        <v>121562435</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2815,21 +2815,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421771</v>
+        <v>421599</v>
       </c>
       <c r="R20" t="n">
-        <v>7051696</v>
+        <v>7051638</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2906,7 +2906,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562423</v>
+        <v>121562425</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421425</v>
+        <v>421399</v>
       </c>
       <c r="R21" t="n">
-        <v>7051623</v>
+        <v>7051705</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562433</v>
+        <v>121562426</v>
       </c>
       <c r="B22" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421634</v>
+        <v>421679</v>
       </c>
       <c r="R22" t="n">
-        <v>7051593</v>
+        <v>7051789</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3089,6 +3089,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3115,7 +3120,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562425</v>
+        <v>121562427</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -3155,10 +3160,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421399</v>
+        <v>421771</v>
       </c>
       <c r="R23" t="n">
-        <v>7051705</v>
+        <v>7051696</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3222,7 +3227,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562424</v>
+        <v>121562423</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3262,10 +3267,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421365</v>
+        <v>421425</v>
       </c>
       <c r="R24" t="n">
-        <v>7051704</v>
+        <v>7051623</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3329,10 +3334,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562426</v>
+        <v>121562433</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3345,21 +3350,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3369,10 +3374,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421679</v>
+        <v>421634</v>
       </c>
       <c r="R25" t="n">
-        <v>7051789</v>
+        <v>7051593</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3405,11 +3410,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3436,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562435</v>
+        <v>121562424</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3452,21 +3452,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421599</v>
+        <v>421365</v>
       </c>
       <c r="R26" t="n">
-        <v>7051638</v>
+        <v>7051704</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 50311-2024 artfynd.xlsx
+++ b/artfynd/A 50311-2024 artfynd.xlsx
@@ -2692,7 +2692,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562422</v>
+        <v>121562425</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421443</v>
+        <v>421399</v>
       </c>
       <c r="R19" t="n">
-        <v>7051615</v>
+        <v>7051705</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562435</v>
+        <v>121562426</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2815,21 +2815,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421599</v>
+        <v>421679</v>
       </c>
       <c r="R20" t="n">
-        <v>7051638</v>
+        <v>7051789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2906,10 +2906,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562425</v>
+        <v>121562435</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421399</v>
+        <v>421599</v>
       </c>
       <c r="R21" t="n">
-        <v>7051705</v>
+        <v>7051638</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,7 +3013,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562426</v>
+        <v>121562427</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421679</v>
+        <v>421771</v>
       </c>
       <c r="R22" t="n">
-        <v>7051789</v>
+        <v>7051696</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3120,7 +3120,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562427</v>
+        <v>121562423</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421771</v>
+        <v>421425</v>
       </c>
       <c r="R23" t="n">
-        <v>7051696</v>
+        <v>7051623</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562423</v>
+        <v>121562422</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421425</v>
+        <v>421443</v>
       </c>
       <c r="R24" t="n">
-        <v>7051623</v>
+        <v>7051615</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562433</v>
+        <v>121562424</v>
       </c>
       <c r="B25" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3350,21 +3350,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421634</v>
+        <v>421365</v>
       </c>
       <c r="R25" t="n">
-        <v>7051593</v>
+        <v>7051704</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3410,6 +3410,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3436,10 +3441,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562424</v>
+        <v>121562433</v>
       </c>
       <c r="B26" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3452,21 +3457,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3476,10 +3481,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421365</v>
+        <v>421634</v>
       </c>
       <c r="R26" t="n">
-        <v>7051704</v>
+        <v>7051593</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3512,11 +3517,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 50311-2024 artfynd.xlsx
+++ b/artfynd/A 50311-2024 artfynd.xlsx
@@ -2692,7 +2692,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562425</v>
+        <v>121562427</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421399</v>
+        <v>421771</v>
       </c>
       <c r="R19" t="n">
-        <v>7051705</v>
+        <v>7051696</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121562435</v>
+        <v>121562424</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421599</v>
+        <v>421365</v>
       </c>
       <c r="R21" t="n">
-        <v>7051638</v>
+        <v>7051704</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,10 +3013,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562427</v>
+        <v>121562433</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421771</v>
+        <v>421634</v>
       </c>
       <c r="R22" t="n">
-        <v>7051696</v>
+        <v>7051593</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3089,11 +3089,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3120,7 +3115,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562423</v>
+        <v>121562425</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -3160,10 +3155,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421425</v>
+        <v>421399</v>
       </c>
       <c r="R23" t="n">
-        <v>7051623</v>
+        <v>7051705</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3334,10 +3329,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562424</v>
+        <v>121562435</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3350,21 +3345,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3374,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421365</v>
+        <v>421599</v>
       </c>
       <c r="R25" t="n">
-        <v>7051704</v>
+        <v>7051638</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3414,7 +3409,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3441,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562433</v>
+        <v>121562423</v>
       </c>
       <c r="B26" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3457,21 +3452,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3481,10 +3476,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421634</v>
+        <v>421425</v>
       </c>
       <c r="R26" t="n">
-        <v>7051593</v>
+        <v>7051623</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3517,6 +3512,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 50311-2024 artfynd.xlsx
+++ b/artfynd/A 50311-2024 artfynd.xlsx
@@ -3329,10 +3329,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121562435</v>
+        <v>121562423</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421599</v>
+        <v>421425</v>
       </c>
       <c r="R25" t="n">
-        <v>7051638</v>
+        <v>7051623</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3436,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562423</v>
+        <v>121562435</v>
       </c>
       <c r="B26" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3452,21 +3452,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421425</v>
+        <v>421599</v>
       </c>
       <c r="R26" t="n">
-        <v>7051623</v>
+        <v>7051638</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 50311-2024 artfynd.xlsx
+++ b/artfynd/A 50311-2024 artfynd.xlsx
@@ -2692,10 +2692,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121562427</v>
+        <v>121562435</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2708,21 +2708,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421771</v>
+        <v>421599</v>
       </c>
       <c r="R19" t="n">
-        <v>7051696</v>
+        <v>7051638</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2799,7 +2799,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121562426</v>
+        <v>121562427</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421679</v>
+        <v>421771</v>
       </c>
       <c r="R20" t="n">
-        <v>7051789</v>
+        <v>7051696</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3013,10 +3013,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121562433</v>
+        <v>121562425</v>
       </c>
       <c r="B22" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421634</v>
+        <v>421399</v>
       </c>
       <c r="R22" t="n">
-        <v>7051593</v>
+        <v>7051705</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3089,6 +3089,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3115,7 +3120,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121562425</v>
+        <v>121562426</v>
       </c>
       <c r="B23" t="n">
         <v>57357</v>
@@ -3155,10 +3160,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421399</v>
+        <v>421679</v>
       </c>
       <c r="R23" t="n">
-        <v>7051705</v>
+        <v>7051789</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3195,7 +3200,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3222,10 +3227,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121562422</v>
+        <v>121562433</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3238,21 +3243,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3262,10 +3267,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421443</v>
+        <v>421634</v>
       </c>
       <c r="R24" t="n">
-        <v>7051615</v>
+        <v>7051593</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3298,11 +3303,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3436,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121562435</v>
+        <v>121562422</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3452,21 +3452,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421599</v>
+        <v>421443</v>
       </c>
       <c r="R26" t="n">
-        <v>7051638</v>
+        <v>7051615</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
